--- a/output/pdf_financials_xlsx/CJT.xlsx
+++ b/output/pdf_financials_xlsx/CJT.xlsx
@@ -2360,55 +2360,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.57762</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3031.764</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>621.522</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>149.976</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>441.506</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="35">
@@ -2476,55 +2476,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.57762</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3031.764</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>621.522</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>149.976</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>441.506</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>94.7</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>31.8</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="37">
@@ -3172,55 +3172,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>16.841094</v>
+        <v>14.263474</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4981.728</v>
+        <v>1949.964</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2156.936</v>
+        <v>1535.414</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>1041.214</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1941.928</v>
+        <v>1791.952</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.10243</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>16.6</v>
+        <v>10.6</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>11.8</v>
+        <v>9.6</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>13.4</v>
+        <v>7.7</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>16.9</v>
+        <v>15.3</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>53.4</v>
+        <v>49.7</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>122.7</v>
+        <v>28</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>14.6</v>
+        <v>8.5</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>153.5</v>
+        <v>121.7</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>44.8</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="49">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -21389,7 +21389,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -26390,7 +26390,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E276" s="5" t="n">

--- a/output/pdf_financials_xlsx/CJT.xlsx
+++ b/output/pdf_financials_xlsx/CJT.xlsx
@@ -2066,34 +2066,34 @@
         <v>4.447209</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>9413.391</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>9067.742</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>9827.694</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>11529.066</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>12.975616</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0</v>
@@ -2124,34 +2124,34 @@
         <v>12.612562</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>5986.205</v>
+        <v>15399.596</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>3795.744</v>
+        <v>12863.486</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>5.066</v>
+        <v>9832.76</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>4.513</v>
+        <v>11533.579</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-12.878051</v>
+        <v>0.097565</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-21.161888</v>
+        <v>11.838112</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>33.6</v>
+        <v>83.3</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>29.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>20.8</v>
+        <v>114.8</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-43.8</v>
@@ -2182,34 +2182,34 @@
         <v>8.784039946239503</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>3.832267019892363</v>
+        <v>9.85856045198358</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>2.293352995469041</v>
+        <v>7.771997835015765</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>3.001700529119339</v>
+        <v>5826.095715496146</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2.573328163488733</v>
+        <v>6576.486520390475</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-6.693451350225644</v>
+        <v>0.05071004773818374</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-7.32245259515571</v>
+        <v>4.096232525951557</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.906344410876133</v>
+        <v>13.59516616314199</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>8.775137111517367</v>
+        <v>21.75502742230347</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>6.440976038689822</v>
+        <v>20.97164211914707</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>4.27455815865187</v>
+        <v>23.59227291409782</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>-6.551982049364248</v>
@@ -6227,37 +6227,37 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>4.447209</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>9413.391</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>9067.742</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>9827.694</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>11529.066</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>12.975616</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>49.7</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="M100" s="3" t="n">
         <v>0</v>
@@ -6926,22 +6926,22 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>257.151</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>958.861</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>289.087</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>246.7</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.183388</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -6950,19 +6950,19 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M112" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N112" s="3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="O112" s="3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="P112" s="3" t="n">
         <v>0</v>
@@ -47069,7 +47069,11 @@
           <t>Proceeds from disposal of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E390" t="inlineStr">
         <is>
           <t>-</t>
@@ -48859,7 +48863,11 @@
           <t>Depreciation of property, plant and equipment 8</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -49655,7 +49663,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E416" t="inlineStr">
         <is>
           <t>-</t>
@@ -51310,7 +51322,11 @@
           <t>Depreciation of property, plant and equipment 5</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -52779,7 +52795,11 @@
           <t>Depreciation of property, plant and equipment 4</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E448" t="inlineStr">
         <is>
           <t>-</t>
@@ -54971,7 +54991,11 @@
           <t>Proceeds from disposal of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E470" t="inlineStr">
         <is>
           <t>-</t>
@@ -55983,7 +56007,11 @@
           <t>Depreciation of property, plant and equipment 5</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E480" t="inlineStr">
         <is>
           <t>-</t>
@@ -58478,7 +58506,11 @@
           <t>Depreciation of property, plant and equipment 6</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E505" t="inlineStr">
         <is>
           <t>-</t>
@@ -64474,7 +64506,11 @@
           <t>Depreciation of property, plant and equipment 7</t>
         </is>
       </c>
-      <c r="D565" t="inlineStr"/>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E565" t="inlineStr">
         <is>
           <t>-</t>
@@ -66189,7 +66225,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E582" s="5" t="n">
@@ -92018,7 +92054,7 @@
       </c>
       <c r="D843" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E843" s="5" t="n">

--- a/output/pdf_financials_xlsx/CJT.xlsx
+++ b/output/pdf_financials_xlsx/CJT.xlsx
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-1.134848</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-2.915755</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -4513,25 +4513,25 @@
         <v>0</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>103.8</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="R70" s="3" t="n">
         <v>0</v>
@@ -4571,25 +4571,25 @@
         <v>0</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>25.2</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>59.3</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>103.8</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>31.4</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="R71" s="3" t="n">
         <v>0</v>
@@ -4803,25 +4803,25 @@
         <v>66.40000000000001</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>29</v>
+        <v>3.8</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>62.9</v>
+        <v>3.6</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>107.4</v>
+        <v>3.6</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>26.5</v>
+        <v>4.5</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>50.1</v>
+        <v>18.7</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>39.3</v>
+        <v>16.4</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>55</v>
+        <v>35.9</v>
       </c>
       <c r="R75" s="3" t="n">
         <v>87.09999999999999</v>
@@ -5107,25 +5107,25 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>1.110261312938177</v>
+        <v>1.27087316762269</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.5900086132644272</v>
+        <v>0.8453919035314384</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.9743589743589743</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.102602010644589</v>
+        <v>0.1351271437019515</v>
       </c>
       <c r="O80" s="3" t="n">
-        <v>0.06927239927841251</v>
+        <v>0.1070354780517138</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.1226258763543658</v>
+        <v>0.1518164435946463</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.1144096516198997</v>
+        <v>0.1403009353395689</v>
       </c>
       <c r="R80" s="1" t="inlineStr">
         <is>
@@ -6672,16 +6672,16 @@
         <v>-15.2</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>-5.8</v>
+        <v>-4.1</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>-12.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>-2.4</v>
+        <v>7.3</v>
       </c>
       <c r="R107" s="3" t="n">
-        <v>-1.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="108">
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>0</v>
+        <v>-1.713173</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -6999,7 +6999,7 @@
         <v>0</v>
       </c>
       <c r="H113" s="3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I113" s="3" t="n">
         <v>0</v>
@@ -7011,7 +7011,7 @@
         <v>0</v>
       </c>
       <c r="L113" s="3" t="n">
-        <v>0</v>
+        <v>-3.1</v>
       </c>
       <c r="M113" s="3" t="n">
         <v>0</v>
@@ -7561,10 +7561,10 @@
         </is>
       </c>
       <c r="B123" s="3" t="n">
-        <v>0</v>
+        <v>10.387608</v>
       </c>
       <c r="C123" s="3" t="n">
-        <v>0</v>
+        <v>3.631969</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -7677,10 +7677,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>-0.722822</v>
+        <v>9.664785999999999</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>-6.913719</v>
+        <v>-3.28175</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -7975,10 +7975,8 @@
       <c r="L129" s="3" t="n">
         <v>74.8</v>
       </c>
-      <c r="M129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M129" s="3" t="n">
+        <v>-162.8</v>
       </c>
       <c r="N129" s="3" t="n">
         <v>140.2</v>
@@ -8308,7 +8306,7 @@
         <v>11.004414</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>11.596046</v>
+        <v>13464.842896</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>15130.098</v>
@@ -8323,7 +8321,7 @@
         <v>-5.846787</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-96.05276600000001</v>
+        <v>-99.3</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>2.2</v>
@@ -8337,10 +8335,8 @@
       <c r="L135" s="3" t="n">
         <v>-67.09999999999999</v>
       </c>
-      <c r="M135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="M135" s="3" t="n">
+        <v>146</v>
       </c>
       <c r="N135" s="3" t="n">
         <v>-46.4</v>
@@ -12141,7 +12137,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -14801,7 +14801,11 @@
           <t>Lease liabilities 2,14</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -39735,7 +39739,11 @@
           <t>Share-based compensation expense 12</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E314" t="inlineStr">
         <is>
           <t>-</t>
@@ -41283,7 +41291,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D330" t="inlineStr"/>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E330" t="inlineStr">
         <is>
           <t>-</t>
@@ -41766,7 +41778,11 @@
           <t>NET CASH GENERATED FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -46982,7 +46998,11 @@
           <t>NET CASH GENERATED FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="D389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E389" t="inlineStr">
         <is>
           <t>-</t>
@@ -49956,7 +49976,11 @@
           <t>Acquisition of business 11</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -50823,7 +50847,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E428" t="inlineStr">
         <is>
           <t>-</t>
@@ -54688,7 +54716,11 @@
           <t>Proceeds from private placement 17,23</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E467" t="inlineStr">
         <is>
           <t>-</t>
@@ -55092,7 +55124,11 @@
           <t>Acquisition of business</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E471" t="inlineStr">
         <is>
           <t>-</t>
@@ -58112,7 +58148,11 @@
           <t>Acquisition of business 8</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
           <t>-</t>
@@ -62025,7 +62065,11 @@
           <t>NET CASH GENERATED BY OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="D540" t="inlineStr"/>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E540" t="inlineStr">
         <is>
           <t>-</t>
@@ -63712,7 +63756,11 @@
           <t>NET CASH GENERATED BY OPERATING ACTIVITIES</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -66728,7 +66776,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D587" t="inlineStr"/>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E587" s="5" t="n">
         <v>-1.912121</v>
       </c>
@@ -67833,7 +67885,11 @@
           <t>Increase in long-term debt</t>
         </is>
       </c>
-      <c r="D598" t="inlineStr"/>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>IssuanceOfDebt</t>
+        </is>
+      </c>
       <c r="E598" s="5" t="n">
         <v>10.387608</v>
       </c>
@@ -68734,7 +68790,11 @@
           <t>Acquisition of business (Note 4)</t>
         </is>
       </c>
-      <c r="D607" t="inlineStr"/>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E607" s="5" t="n">
         <v>-1.713173</v>
       </c>
@@ -92965,7 +93025,11 @@
           <t>LOSS FROM DISCONTINUED OPERATIONS (NOTE 4)</t>
         </is>
       </c>
-      <c r="D852" t="inlineStr"/>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E852" s="5" t="n">
         <v>-1.134848</v>
       </c>
